--- a/Assets/test260903/chapter0201.xlsx
+++ b/Assets/test260903/chapter0201.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C65FED-FE1B-4CBD-8F0E-560A3B393131}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0201" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0201" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="137">
   <si>
     <t>Command</t>
   </si>
@@ -76,27 +85,604 @@
   </si>
   <si>
     <t>*chapter0202_Start</t>
+  </si>
+  <si>
+    <t>202X年、九州北部に公営カジノが完成。
+賭博の街として、急速な発展を遂げる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：黒</t>
+  </si>
+  <si>
+    <t>同時に、
+世界最悪の犯罪都市になった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>現状、この街の最大派閥は、
+中国系マフィアの「白蛇」である</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>白蛇は違法な商売だけではなく、
+表の仕事も行っていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>高い戦闘能力を持つ人材による、
+「要人警護」である。そして……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「その街」へ飛ぶ少年が1人。
+彼はひとり、飛行機の中で考えていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：旅客機の機内</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>機内環境音</t>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……僕の今回の旅の目的は、
+叔父を訪ねること。そして……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>父さんが経営に噛んでいるカジノの、
+新店舗の建設工事が予定より遅れている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>管理者の現地支社長……僕の叔父に、
+遅延理由を説明してもらう</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕は説明を聞いた後、叔父に対して
+予定日に遅れないようにと念を押す</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ただし、「念を押す」と言っても、
+「命令」や「催促」はしてはいけない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あくまで親戚を訪ねてきた甥として、
+最後まで、にこやかに過ごすんだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……何とも回りくどい。
+同族企業の悪いところが出ている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>工事の遅延の原因が知りたいなら、
+資料を取り寄せ、精査すればいい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>開店予定日の死守も、
+電話一本で命令すれば十分だろう</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>けれど父さんは、この「催促」を
+「業務」にはしなかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>甥が叔父を訪ね、雑談をする中で、
+新店舗の件について触れる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「業務」ではないから、
+公式の記録も残らない。単なる雑談だ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>これなら叔父の経歴に「工事が遅延し、
+注意を受けた」という事実は残らない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして息子の僕が派遣されるのは、
+叔父に対して「礼」を見せるためだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>立場のある人間を送ることで、
+叔父の下請け感を軽減する</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>肩書きだけなら、父は叔父より上だ。
+しかし、血縁関係は異なる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>叔父に対して礼を欠けば、
+それ以外の親戚たちにも影響が出る</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いわば、父が叔父の機嫌を取るために
+僕は飛ばされているのだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>こうして事実を整理して考えるほど、
+使いっ走りのようで、腹が立つ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>父さんは都合のいいときだけ、
+僕を「息子」「長男」扱いする</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>普段は「前妻の子」として、
+弟たちとは明確に区別しているくせに</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……いや、考えるのはやめよう。
+怒ったところで、血筋は変わらない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>今はまだ我慢するべきだ。
+僕はまだ15歳で、社内に肩書きもない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕が重役に就くのは、
+急いでも大学を卒業してからになる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それまでは、
+こうした小間使いに徹しておくべきだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>目的地までの間に余計なものを……
+つまり何も見たくなかったからだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして少年は、
+「その街」へ降り立ったが……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>自尊心と野望に折り合いをつけると、
+少年は瞼をそっと閉じた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>StopSe</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……え？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ヨシッ！　1名様、ご到着～♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：空港</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシ、
+護衛の鈴野美鈴（すずの みれい）！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>余計な真似をしなかったら、
+君の安全は保障しよー！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>逆に、余計な真似をしやがったら、
+保障は一切しねぇ！　つーかできねー！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……はい。まずココまでOK？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……これが、僕の護衛？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>確かに銃は持っているし、
+肉体も凄まじい鍛え方をしているようだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>しかし……こんなギャルが護衛？
+冗談だろ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>お～～い、ガキンチョくん。
+さっさと質問に答えろってば</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>怒り</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>主人公</t>
+  </si>
+  <si>
+    <t>やり方を理解したかって聞いてんの！
+Yes か No で答えろよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-1-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-1-ｂ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>君……何の冗談だ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>理解できない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はぁ……ったく、
+これだからガキは嫌い！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-1合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マジで？
+かな～～り簡単に説明したのに？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ま、分かってねーなら、
+それはそれでいいわ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>車で話せばいいから。
+さっさと片付けたいから、乗って乗って</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシの愛しき特注ハマー♪
+強いぞ固いぞカッケーぞ♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……頑丈そうな車に乗せられた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：車内（ハマー）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>車はちゃんと護衛用だけど、
+やっぱり納得がいかない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシをジロジロ見てるけど……何？
+どうかした？　車に酔った？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あっ、もしかして……思春期！？　
+性の芽生え！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>デカいカジノ会社の御曹司って、
+話は聞いていたけれど……な～んだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ただのエロガキってわけか～！
+アハハハ、残念でした！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシは護衛だから！
+エロいことは無し！　OK？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-2-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-2-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バカバカしい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>発想に品性がない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「バカ」って言ったか……上等っ。
+アタシにそんな口を利くとはね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-2合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ほうほう、品性がないね。
+なるほどねぇ……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エロガキ、
+もう一回だけチャンスをあげる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>さっきの質問だけど、
+今度はちゃんと答えてね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシの言う通りにして。
+余計な真似はすんじゃねーぞ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>邪魔をしねぇ、文句は言わねぇ、
+アタシの言うことには従う</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エロガキ、わかった？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-3-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-3-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エロガキって？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>雇い主は僕だぞ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はい、ブーッ！！！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ぐわぁ……！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Shake</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-3合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>x=3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>イテテ……頭のてっぺんを、
+ゲンコツで思い切り殴られた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちゃんと答えろっての！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>シツケはゲンコツ主義だから！
+よく考えること！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-4-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ぼ、僕は雇い主だぞ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>うるせーな！
+ここではアタシがルールなの！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>つーかアタシの方が年上だし！
+人生の先輩は、敬うもんでしょ！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……なんだコイツ、メチャクチャだ。
+こんなヤツが護衛なのか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>護衛のくせに、僕を殴った。
+この僕を……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>不服そうな目をして……上等♪
+もう一発ブン殴ってやろうか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ひねくれたエロガキのシツケは、
+命令にないけど、特別サービス！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アンタを何発でもブン殴って、
+根性叩き直してやるよ！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バカで体罰肯定論者だ。話が通じない。
+ここで逆らうのは得策じゃない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バカに正論は通じないからだ。
+こういう時は適当に話を逸らすん</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-5-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>おっ、エロガキ……！
+案外に見る目があるじゃん♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そ、その服、変わってますね</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +690,73 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +946,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1065"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,702 +1005,1288 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="7"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
+    <row r="8" spans="1:12" ht="30" customHeight="1">
+      <c r="I8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I10" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" customHeight="1">
+      <c r="I12" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
+    <row r="13" spans="1:12" ht="28.8" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
+    <row r="16" spans="1:12" ht="30" customHeight="1">
+      <c r="B16" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="28.8" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
+      <c r="B17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" customHeight="1">
       <c r="A20" s="1"/>
+      <c r="B20" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
+      <c r="I20" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B21" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
+      <c r="I21" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" customHeight="1">
+      <c r="B22" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
+      <c r="I22" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="B23" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" spans="1:10" ht="28.2" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="B24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
+    <row r="25" spans="1:10" ht="27" customHeight="1">
+      <c r="B25" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
+      <c r="I25" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B26" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
+      <c r="I26" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="B27" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" spans="1:10" ht="30.6" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="B28" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
+    <row r="29" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B30" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B31" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B32" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B36" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B37" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
+      <c r="I37" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1">
+      <c r="B38" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
+      <c r="I38" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B39" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B40" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="I40" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I43" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="30" customHeight="1">
+      <c r="I44" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="30" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I46" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I47" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="28.2" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
+      <c r="B50" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="B51" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B52" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="I54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="28.8" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
+      <c r="B55" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1">
+      <c r="B57" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B58" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A59" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
+    <row r="62" spans="1:10" ht="30" customHeight="1">
+      <c r="B62" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A64" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="B64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="1"/>
+    <row r="65" spans="1:9" ht="30" customHeight="1">
+      <c r="B65" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
+    <row r="68" spans="1:9" ht="30" customHeight="1">
+      <c r="B68" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.8" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
+      <c r="B69" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A70" s="1"/>
+      <c r="B70" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A71" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B72" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
+      <c r="I72" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="31.2" customHeight="1">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
+      <c r="I73" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B76" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B77" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B78" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A79" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A80" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="I80" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+    <row r="82" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B82" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B85" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
+    <row r="88" spans="1:10" ht="30" customHeight="1">
+      <c r="A88" s="1"/>
+      <c r="B88" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="31.2" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
+      <c r="B89" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="30.6" customHeight="1">
       <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
+      <c r="B90" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B91" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B92" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
+      <c r="I93" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
+      <c r="I94" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="B95" s="1"/>
     </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B100" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" ht="13.5" customHeight="1">
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" ht="13.5" customHeight="1">
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="1"/>
+      <c r="B102" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="30" customHeight="1">
+      <c r="A103" s="1"/>
+      <c r="B103" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B104" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B105" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A106" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="I109" s="1"/>
-    </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
+    <row r="108" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B108" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B109" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="30" customHeight="1">
+      <c r="B110" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
+      <c r="I110" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B111" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B112" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B113" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="30" customHeight="1">
+      <c r="B114" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B115" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="1"/>
+      <c r="I115" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="30" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
+      <c r="I116" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A117" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C117" s="1"/>
+      <c r="I117" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="30" customHeight="1">
+      <c r="B119" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
       <c r="I120" s="1"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
       <c r="I121" s="1"/>
-    </row>
-    <row r="122" ht="13.5" customHeight="1">
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A124" s="1"/>
       <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+      <c r="C126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="C131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A136" s="1"/>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="H138" s="1"/>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+      <c r="H139" s="1"/>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="148" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="149" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="161" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="162" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="163" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="164" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A164" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="166" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="167" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="168" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="169" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="170" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="171" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="172" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -1973,10 +3169,16 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0201.xlsx
+++ b/Assets/test260903/chapter0201.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C65FED-FE1B-4CBD-8F0E-560A3B393131}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C052A25E-ACEE-47AD-A3CE-9259CC2974B8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="185">
   <si>
     <t>Command</t>
   </si>
@@ -628,6 +628,217 @@
   </si>
   <si>
     <t>そ、その服、変わってますね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>これ、オーダーメイドなんだよね～！
+よく出来てるでしょ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ふぅ……どうやら
+話題を逸らすことには成功したようだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>けれど、服について深堀されても困る。
+確かに仕立ては良さそうだけど</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そもそも、この人は護衛だ。
+この街では拳銃の所持が解禁されている</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>銃撃戦は日常茶飯事だし、
+いわゆる誘拐ビジネスも盛んだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そんな街の護衛なのに……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>薄着すぎませんか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-6-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>まぁね。
+でも、ちょうどいいハンデだよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-7-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ハンデ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そうそう、ハンデよ。
+この格好なら、分かりやすいじゃん？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「あの女のここを撃ったら死ぬ」って、
+バカでも一発で分かるからさ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アタシは反則レベルで強いわけ。
+だから雑魚の相手にはハンデが要る</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>これくらいのハンデつけねーと、
+さっぱり緊張しねーし、楽しくねーし</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>自分に喝を入れる為にもハンデが要る。
+分かる？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-8-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>わ……分からない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アハハハ、分かんないか。
+ま、エロガキは貧弱そうだし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>こういう強者の理論は分からない……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ん？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エロガキ、伏せて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-9-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>伏せて！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いて！　またゲンコツをくらった……！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>何をするんですか……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0201-10-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>えっ……！
+い、今のは……銃声！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それに銃声のした方から、
+大柄な男たちが迫ってくる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フフフ……さっそく来た来た♪
+エロガキ狙いの襲撃だよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>しゅ、襲撃～！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>お前をさらって、金に換えるか。
+もしくは、ここでお前の首をはねるか</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ええっ……！？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フフッ……話が早い。
+エロガキのシツケより、こっちが好き♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>笑ってる場合じゃないでしょ！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>打死你（ダァスゥニィ）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>女は、銃を構えて車から飛び出した。
+そして少年は目撃した</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>車のドア</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>彼女が、どれほどの強者であるかを</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>銃撃戦（連射）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>今のは中国語。
+意味は「ブッ殺す」！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>black</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -705,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -733,6 +944,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1065"/>
+  <dimension ref="A1:L1073"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1949,88 +2163,87 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="12" t="s">
+      <c r="A101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C101" s="10"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B102" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="12" t="s">
+      <c r="C102" s="10"/>
+      <c r="D102" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="1"/>
-      <c r="B102" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="30" customHeight="1">
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I103" s="13" t="s">
+      <c r="I103" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="30" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="B104" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I104" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B104" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I104" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="31.2" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
       <c r="B105" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I105" s="5" t="s">
+      <c r="I105" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B106" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A106" s="12" t="s">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I106" s="12" t="s">
+      <c r="I107" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A107" s="1" t="s">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B108" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="30.6" customHeight="1">
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" ht="27.6" customHeight="1">
       <c r="B109" s="10" t="s">
         <v>65</v>
       </c>
@@ -2038,35 +2251,35 @@
         <v>74</v>
       </c>
       <c r="I109" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B110" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I110" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="30" customHeight="1">
-      <c r="B110" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="I110" s="5" t="s">
+    <row r="111" spans="1:9" ht="30" customHeight="1">
+      <c r="B111" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="I111" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B111" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I111" s="5" t="s">
+    <row r="112" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B112" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112" s="5" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B112" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="28.8" customHeight="1">
@@ -2077,10 +2290,10 @@
         <v>63</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="30" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="28.8" customHeight="1">
       <c r="B114" s="10" t="s">
         <v>65</v>
       </c>
@@ -2088,205 +2301,539 @@
         <v>63</v>
       </c>
       <c r="I114" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="30" customHeight="1">
+      <c r="B115" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I115" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B115" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="I115" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="30" customHeight="1">
-      <c r="B116" s="1"/>
+    <row r="116" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B116" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C116" s="1"/>
       <c r="I116" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A117" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>134</v>
-      </c>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="30" customHeight="1">
+      <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="I117" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="I118" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A118" s="1" t="s">
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="30" customHeight="1">
-      <c r="B119" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C119" s="9" t="s">
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" ht="30" customHeight="1">
+      <c r="B120" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C120" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I119" s="5" t="s">
+      <c r="I120" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="30.6" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="I121" s="1"/>
+      <c r="B121" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
+    <row r="122" spans="1:10" ht="28.8" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="I122" s="1"/>
+      <c r="B122" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+    <row r="123" spans="1:10" ht="30" customHeight="1">
+      <c r="A123" s="1"/>
+      <c r="B123" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:10" ht="30" customHeight="1">
+      <c r="B124" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="I124" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="28.8" customHeight="1">
       <c r="A125" s="1"/>
+      <c r="B125" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I125" s="13" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="I126" s="1"/>
+      <c r="A126" s="1"/>
+      <c r="B126" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126" s="13" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B127" s="1"/>
+      <c r="A127" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="C127" s="1"/>
-      <c r="I127" s="1"/>
+      <c r="I127" s="13" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
+    <row r="129" spans="1:10" ht="30" customHeight="1">
+      <c r="B129" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
+      <c r="A130" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A131" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
       <c r="I131" s="1"/>
-    </row>
-    <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B132" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B133" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="30.6" customHeight="1">
       <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A136" s="1"/>
+      <c r="B134" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I134" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I135" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="30" customHeight="1">
+      <c r="B136" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="137" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A137" s="1"/>
+      <c r="A137" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="138" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="30.6" customHeight="1">
       <c r="A139" s="1"/>
+      <c r="B139" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
+      <c r="I139" s="5" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I140" s="1"/>
+      <c r="A140" s="1"/>
+      <c r="B140" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H140" s="1"/>
+      <c r="I140" s="5" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I141" s="1"/>
+      <c r="B141" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I142" s="1"/>
+      <c r="B142" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I143" s="1"/>
+      <c r="A143" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A144" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="I144" s="1"/>
     </row>
-    <row r="145" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="148" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="149" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="161" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="162" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="163" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="164" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A164" s="1" t="s">
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B145" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B146" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A147" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I147" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A148" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C150" s="10"/>
+      <c r="D150" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B151" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I151" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B152" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="30" customHeight="1">
+      <c r="B153" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I153" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B154" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B155" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I155" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B156" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I156" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B157" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I157" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B158" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I158" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B159" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I159" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B160" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I160" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B161" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I161" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I162" s="13"/>
+    </row>
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="6"/>
+      <c r="B163" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I163" s="13"/>
+    </row>
+    <row r="164" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I164" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A165" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I165" s="13"/>
+    </row>
+    <row r="166" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A166" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="I166" s="13"/>
+    </row>
+    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I167" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="171" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A172" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="166" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="167" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="168" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="169" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="170" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="171" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="172" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="173" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="174" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="175" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="176" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -3176,6 +3723,14 @@
     <row r="1063" ht="13.5" customHeight="1"/>
     <row r="1064" ht="13.5" customHeight="1"/>
     <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
+    <row r="1071" ht="13.5" customHeight="1"/>
+    <row r="1072" ht="13.5" customHeight="1"/>
+    <row r="1073" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0201.xlsx
+++ b/Assets/test260903/chapter0201.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C052A25E-ACEE-47AD-A3CE-9259CC2974B8}"/>
+  <xr:revisionPtr revIDLastSave="511" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB8453C-371B-48B1-85CB-F4E63CEE966D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="186">
   <si>
     <t>Command</t>
   </si>
@@ -613,11 +613,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>バカに正論は通じないからだ。
-こういう時は適当に話を逸らすん</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>*選択肢0201-5-a</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -839,6 +834,16 @@
   </si>
   <si>
     <t>black</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして204X年、九州北部は
+アジア最大の歓楽街となったが……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バカに正論は通じないからだ。
+こういう時は適当に話を逸らすんだ</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1167,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1073"/>
+  <dimension ref="A1:L1075"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1295,77 +1300,75 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="28.8" customHeight="1">
+    <row r="9" spans="1:12" ht="30" customHeight="1">
       <c r="I9" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28.2" customHeight="1">
-      <c r="I10" s="5" t="s">
+    <row r="11" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="28.8" customHeight="1">
-      <c r="I11" s="5" t="s">
+    <row r="12" spans="1:12" ht="28.8" customHeight="1">
+      <c r="I12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1">
-      <c r="I12" s="5" t="s">
+    <row r="13" spans="1:12" ht="30" customHeight="1">
+      <c r="I13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="28.8" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" ht="28.8" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="30" customHeight="1">
-      <c r="B16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="I16" s="5" t="s">
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1">
+      <c r="B17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="I17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="28.8" customHeight="1">
       <c r="A18" s="1"/>
@@ -1373,150 +1376,151 @@
         <v>75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="11" t="s">
         <v>75</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="28.8" customHeight="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="1"/>
       <c r="I20" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="I21" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1">
+    <row r="22" spans="1:10" ht="28.8" customHeight="1">
       <c r="B22" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="1"/>
       <c r="I22" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="B23" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="I23" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="28.2" customHeight="1">
+    <row r="24" spans="1:10" ht="30" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="11" t="s">
         <v>75</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="27" customHeight="1">
-      <c r="B25" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="I25" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="B26" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="1"/>
       <c r="I26" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B27" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="I27" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="30.6" customHeight="1">
+    <row r="28" spans="1:10" ht="28.8" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="11" t="s">
         <v>75</v>
       </c>
       <c r="I28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B29" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B30" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B30" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I30" s="5" t="s">
+    <row r="31" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B31" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B31" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I31" s="5" t="s">
+    <row r="32" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B32" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B32" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I32" s="5" t="s">
+    <row r="33" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B33" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I33" s="5" t="s">
+    <row r="34" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I34" s="5" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B34" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="28.8" customHeight="1">
@@ -1524,7 +1528,7 @@
         <v>75</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="28.8" customHeight="1">
@@ -1532,122 +1536,121 @@
         <v>75</v>
       </c>
       <c r="I36" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B37" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B37" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="I37" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1">
+    <row r="38" spans="1:9" ht="31.2" customHeight="1">
       <c r="B38" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="1"/>
       <c r="I38" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30" customHeight="1">
+      <c r="B39" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="I39" s="5" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B39" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="28.8" customHeight="1">
       <c r="B40" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="11"/>
       <c r="I40" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B41" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="I41" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A41" s="10" t="s">
+    <row r="42" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A42" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B42" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="5"/>
-    </row>
-    <row r="42" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A42" s="9" t="s">
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A43" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B43" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I42" s="5"/>
-    </row>
-    <row r="43" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I44" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" customHeight="1">
-      <c r="I44" s="5" t="s">
+    <row r="45" spans="1:9" ht="30" customHeight="1">
+      <c r="I45" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30" customHeight="1">
-      <c r="A45" s="9" t="s">
+    <row r="46" spans="1:9" ht="30" customHeight="1">
+      <c r="A46" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="5"/>
-    </row>
-    <row r="46" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I47" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I47" s="5" t="s">
+    <row r="48" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B48" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A48" s="10" t="s">
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B49" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I48" s="5"/>
-    </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="12" t="s">
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="30" customHeight="1">
+    <row r="51" spans="1:10" ht="28.2" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="10" t="s">
         <v>65</v>
@@ -1656,11 +1659,11 @@
         <v>63</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" ht="28.8" customHeight="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" customHeight="1">
+      <c r="A52" s="1"/>
       <c r="B52" s="10" t="s">
         <v>65</v>
       </c>
@@ -1668,63 +1671,64 @@
         <v>63</v>
       </c>
       <c r="I52" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B53" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B53" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="12" t="s">
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I54" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B54" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="I54" s="5" t="s">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="I55" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" ht="30" customHeight="1">
+    <row r="56" spans="1:10" ht="28.8" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="11" t="s">
         <v>75</v>
       </c>
       <c r="I56" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="30" customHeight="1">
-      <c r="B57" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="30.6" customHeight="1">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="30" customHeight="1">
       <c r="B58" s="10" t="s">
         <v>65</v>
       </c>
@@ -1732,18 +1736,18 @@
         <v>74</v>
       </c>
       <c r="I58" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B59" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I59" s="5" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A59" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1">
@@ -1751,87 +1755,86 @@
         <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A61" s="1" t="s">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1">
-      <c r="B62" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" s="10" t="s">
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1">
+      <c r="B63" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I63" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A63" s="12" t="s">
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A64" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A64" s="1" t="s">
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A65" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" ht="30" customHeight="1">
-      <c r="B65" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="B65" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" ht="30" customHeight="1">
+      <c r="B66" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I65" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A66" s="12" t="s">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A67" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="1:9" ht="30" customHeight="1">
-      <c r="B68" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A69" s="1"/>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" ht="30" customHeight="1">
       <c r="B69" s="10" t="s">
         <v>65</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>87</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28.8" customHeight="1">
@@ -1847,89 +1850,92 @@
       <c r="B70" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A71" s="1"/>
+      <c r="B71" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="5" t="s">
+      <c r="H71" s="1"/>
+      <c r="I71" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A71" s="10" t="s">
+    <row r="72" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A72" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A73" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B73" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="5"/>
-    </row>
-    <row r="72" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B72" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="I72" s="5" t="s">
+      <c r="C73" s="9"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="5"/>
+    </row>
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B74" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="I74" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="5" t="s">
+    <row r="75" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B75" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="I75" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30" customHeight="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C74" s="10" t="s">
+    <row r="76" spans="1:9" ht="30" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I76" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B76" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="30.6" customHeight="1">
+    <row r="77" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A77" s="1"/>
       <c r="B77" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>63</v>
       </c>
+      <c r="H77" s="1"/>
       <c r="I77" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="28.8" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="30.6" customHeight="1">
       <c r="B78" s="10" t="s">
         <v>65</v>
       </c>
@@ -1937,123 +1943,119 @@
         <v>63</v>
       </c>
       <c r="I78" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B79" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B80" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I80" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A79" s="12" t="s">
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I81" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A80" s="12" t="s">
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="I80" s="5" t="s">
+      <c r="C82" s="1"/>
+      <c r="I82" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B82" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A83" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B84" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A85" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="31.2" customHeight="1">
-      <c r="B85" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C85" s="10" t="s">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B87" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I85" s="5" t="s">
+      <c r="I87" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A86" s="12" t="s">
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A88" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A87" s="1" t="s">
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A89" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="30" customHeight="1">
-      <c r="A88" s="1"/>
-      <c r="B88" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="30" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="10" t="s">
         <v>65</v>
@@ -2061,11 +2063,13 @@
       <c r="C90" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I90" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A91" s="1"/>
       <c r="B91" s="10" t="s">
         <v>65</v>
       </c>
@@ -2073,65 +2077,73 @@
         <v>74</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+        <v>106</v>
+      </c>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A92" s="1"/>
       <c r="B92" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I92" s="5" t="s">
+      <c r="I92" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B93" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B94" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I94" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A93" s="12" t="s">
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="I93" s="5" t="s">
+      <c r="C95" s="1"/>
+      <c r="I95" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C94" s="1"/>
-      <c r="I94" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="A96" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="I96" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="I97" s="1"/>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="12" t="s">
@@ -2140,171 +2152,165 @@
       <c r="B98" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="1"/>
-      <c r="I98" s="1"/>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B100" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C100" s="10" t="s">
+      <c r="A100" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B102" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="6" t="s">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="12" t="s">
+      <c r="B103" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103" s="10"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B104" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C102" s="10"/>
-      <c r="D102" s="12" t="s">
+      <c r="C104" s="10"/>
+      <c r="D104" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="1"/>
-      <c r="B103" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I103" s="12" t="s">
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="1"/>
+      <c r="B105" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I105" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" customHeight="1">
-      <c r="A104" s="1"/>
-      <c r="B104" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I104" s="13" t="s">
+    <row r="106" spans="1:9" ht="30" customHeight="1">
+      <c r="A106" s="1"/>
+      <c r="B106" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I106" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B105" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C105" s="10" t="s">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B107" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I105" s="12" t="s">
+      <c r="I107" s="12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B106" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C106" s="10" t="s">
+    <row r="108" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B108" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I106" s="5" t="s">
+      <c r="I108" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A107" s="12" t="s">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A109" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I107" s="12" t="s">
+      <c r="I109" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="1" t="s">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B109" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C109" s="10" t="s">
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B111" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C111" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I109" s="5" t="s">
+      <c r="I111" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B110" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C110" s="10" t="s">
+    <row r="112" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B112" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I110" s="5" t="s">
+      <c r="I112" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="30" customHeight="1">
-      <c r="B111" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="I111" s="5" t="s">
+    <row r="113" spans="1:10" ht="30" customHeight="1">
+      <c r="B113" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="I113" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B112" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I112" s="5" t="s">
+    <row r="114" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B114" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I114" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B113" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B114" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="30" customHeight="1">
+    <row r="115" spans="1:10" ht="28.8" customHeight="1">
       <c r="B115" s="10" t="s">
         <v>65</v>
       </c>
@@ -2312,395 +2318,400 @@
         <v>63</v>
       </c>
       <c r="I115" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B116" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="30" customHeight="1">
+      <c r="B117" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I117" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B116" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="I116" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="30" customHeight="1">
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="I117" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A118" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>134</v>
+    <row r="118" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B118" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="C118" s="1"/>
       <c r="I118" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A119" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B119" s="1"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="30" customHeight="1">
+      <c r="B119" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="C119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="30" customHeight="1">
-      <c r="B120" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C120" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="I119" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C120" s="1"/>
       <c r="I120" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A121" s="1"/>
-      <c r="B121" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C121" s="9" t="s">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" ht="30" customHeight="1">
+      <c r="B122" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C122" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I121" s="5" t="s">
+      <c r="I122" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A123" s="1"/>
+      <c r="B123" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A124" s="1"/>
+      <c r="B124" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I124" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A122" s="1"/>
-      <c r="B122" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I122" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="30" customHeight="1">
-      <c r="A123" s="1"/>
-      <c r="B123" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I123" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="30" customHeight="1">
-      <c r="B124" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C124" s="1"/>
-      <c r="I124" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="28.8" customHeight="1">
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" ht="30" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I125" s="13" t="s">
+      <c r="I125" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="30" customHeight="1">
+      <c r="B126" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="I126" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A127" s="1"/>
+      <c r="B127" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I127" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I128" s="13" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
-      <c r="B126" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I126" s="13" t="s">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A129" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C129" s="1"/>
+      <c r="I129" s="13" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A127" s="12" t="s">
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:10" ht="30" customHeight="1">
+      <c r="B131" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A132" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C127" s="1"/>
-      <c r="I127" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A128" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" spans="1:10" ht="30" customHeight="1">
-      <c r="B129" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I129" s="5" t="s">
+      <c r="B132" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B130" s="1" t="s">
+      <c r="I132" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="I130" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A131" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-    </row>
-    <row r="132" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B132" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I132" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B133" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I133" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A134" s="1"/>
+    </row>
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="28.8" customHeight="1">
       <c r="B134" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I134" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A135" s="1"/>
+      <c r="I134" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="28.2" customHeight="1">
       <c r="B135" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I135" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="30" customHeight="1">
+      <c r="I135" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A136" s="1"/>
       <c r="B136" s="10" t="s">
         <v>65</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="I136" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A137" s="1"/>
+      <c r="B137" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I137" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="30" customHeight="1">
+      <c r="B138" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A137" s="12" t="s">
+      <c r="I139" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A141" s="1"/>
+      <c r="B141" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H141" s="1"/>
+      <c r="I141" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1"/>
+      <c r="B142" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H142" s="1"/>
+      <c r="I142" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B143" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B144" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A145" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I137" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A138" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A139" s="1"/>
-      <c r="B139" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C139" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H139" s="1"/>
-      <c r="I139" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A140" s="1"/>
-      <c r="B140" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C140" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H140" s="1"/>
-      <c r="I140" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B141" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B142" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C142" s="10" t="s">
+      <c r="B145" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A146" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B147" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C147" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I142" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A143" s="12" t="s">
+      <c r="I147" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B148" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A149" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A144" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I144" s="1"/>
-    </row>
-    <row r="145" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B145" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I145" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B146" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I146" s="5" t="s">
+      <c r="B149" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I149" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A147" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B147" s="1" t="s">
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A151" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A152" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C152" s="10"/>
+      <c r="D152" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B153" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I153" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="I147" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A148" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A149" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A150" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C150" s="10"/>
-      <c r="D150" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B151" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I151" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B152" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I152" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" ht="30" customHeight="1">
-      <c r="B153" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C153" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I153" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+    </row>
+    <row r="154" spans="1:9" ht="28.2" customHeight="1">
       <c r="B154" s="14" t="s">
         <v>75</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="28.8" customHeight="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="30" customHeight="1">
       <c r="B155" s="10" t="s">
         <v>65</v>
       </c>
@@ -2708,7 +2719,7 @@
         <v>63</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="13.5" customHeight="1">
@@ -2716,10 +2727,10 @@
         <v>75</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="30.6" customHeight="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="28.8" customHeight="1">
       <c r="B157" s="10" t="s">
         <v>65</v>
       </c>
@@ -2727,7 +2738,7 @@
         <v>63</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="13.5" customHeight="1">
@@ -2735,10 +2746,10 @@
         <v>75</v>
       </c>
       <c r="I158" s="13" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="30.6" customHeight="1">
       <c r="B159" s="10" t="s">
         <v>65</v>
       </c>
@@ -2746,7 +2757,7 @@
         <v>63</v>
       </c>
       <c r="I159" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="13.5" customHeight="1">
@@ -2754,10 +2765,10 @@
         <v>75</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="28.8" customHeight="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
       <c r="B161" s="10" t="s">
         <v>65</v>
       </c>
@@ -2765,73 +2776,90 @@
         <v>63</v>
       </c>
       <c r="I161" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B162" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I162" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B163" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I163" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A164" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I164" s="13"/>
+    </row>
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A165" s="6"/>
+      <c r="B165" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I165" s="13"/>
+    </row>
+    <row r="166" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I166" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A167" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B167" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="I167" s="13"/>
+    </row>
+    <row r="168" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A168" s="10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A162" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B162" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="I162" s="13"/>
-    </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C163" s="9" t="s">
+      <c r="B168" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="I168" s="13"/>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I169" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="I163" s="13"/>
-    </row>
-    <row r="164" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I164" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A165" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B165" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="I165" s="13"/>
-    </row>
-    <row r="166" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A166" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G166">
-        <v>1</v>
-      </c>
-      <c r="I166" s="13"/>
-    </row>
-    <row r="167" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I167" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1"/>
+    </row>
     <row r="170" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="171" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A172" s="1" t="s">
+    <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A174" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B174" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
@@ -3731,6 +3759,8 @@
     <row r="1071" ht="13.5" customHeight="1"/>
     <row r="1072" ht="13.5" customHeight="1"/>
     <row r="1073" ht="13.5" customHeight="1"/>
+    <row r="1074" ht="13.5" customHeight="1"/>
+    <row r="1075" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0201.xlsx
+++ b/Assets/test260903/chapter0201.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB8453C-371B-48B1-85CB-F4E63CEE966D}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9C2D9F3-B43B-468F-9886-1765A563637F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="186">
   <si>
     <t>Command</t>
   </si>
@@ -1172,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1075"/>
+  <dimension ref="A1:L1076"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -2652,215 +2652,224 @@
       </c>
     </row>
     <row r="148" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B148" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I148" s="5" t="s">
+      <c r="A148" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C148" s="10"/>
+      <c r="I148" s="5"/>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B149" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I149" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A149" s="12" t="s">
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I149" s="5" t="s">
+      <c r="I150" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A150" s="1" t="s">
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A151" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A151" s="6" t="s">
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A152" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B152" s="12" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A152" s="12" t="s">
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A153" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B153" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C152" s="10"/>
-      <c r="D152" s="12" t="s">
+      <c r="C153" s="10"/>
+      <c r="D153" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B153" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I153" s="13" t="s">
+    <row r="154" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B154" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154" s="13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B154" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I154" s="13" t="s">
+    <row r="155" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B155" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I155" s="13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="30" customHeight="1">
-      <c r="B155" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C155" s="9" t="s">
+    <row r="156" spans="1:9" ht="30" customHeight="1">
+      <c r="B156" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C156" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I155" s="13" t="s">
+      <c r="I156" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B156" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I156" s="13" t="s">
+    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B157" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I157" s="13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B157" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C157" s="9" t="s">
+    <row r="158" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B158" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C158" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I157" s="13" t="s">
+      <c r="I158" s="13" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B158" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I158" s="13" t="s">
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B159" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I159" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B159" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C159" s="9" t="s">
+    <row r="160" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B160" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C160" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I159" s="13" t="s">
+      <c r="I160" s="13" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B160" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I160" s="13" t="s">
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B161" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I161" s="13" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B161" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C161" s="9" t="s">
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B162" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C162" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I161" s="13" t="s">
+      <c r="I162" s="13" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B162" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I162" s="13" t="s">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B163" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I163" s="13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B163" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C163" s="9" t="s">
+    <row r="164" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B164" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C164" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I163" s="13" t="s">
+      <c r="I164" s="13" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A164" s="6" t="s">
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A165" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B165" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I164" s="13"/>
-    </row>
-    <row r="165" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C165" s="9" t="s">
+      <c r="I165" s="13"/>
+    </row>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A166" s="6"/>
+      <c r="B166" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C166" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="I165" s="13"/>
-    </row>
-    <row r="166" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I166" s="13" t="s">
+      <c r="I166" s="13"/>
+    </row>
+    <row r="167" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I167" s="13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A167" s="11" t="s">
+    <row r="168" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A168" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B168" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I167" s="13"/>
-    </row>
-    <row r="168" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A168" s="10" t="s">
+      <c r="I168" s="13"/>
+    </row>
+    <row r="169" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A169" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B169" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="G168">
+      <c r="G169">
         <v>1</v>
       </c>
-      <c r="I168" s="13"/>
-    </row>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I169" s="13" t="s">
+      <c r="I169" s="13"/>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I170" s="13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="171" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A174" s="1" t="s">
+    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A175" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="B175" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
@@ -3761,6 +3770,7 @@
     <row r="1073" ht="13.5" customHeight="1"/>
     <row r="1074" ht="13.5" customHeight="1"/>
     <row r="1075" ht="13.5" customHeight="1"/>
+    <row r="1076" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0201.xlsx
+++ b/Assets/test260903/chapter0201.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9C2D9F3-B43B-468F-9886-1765A563637F}"/>
+  <xr:revisionPtr revIDLastSave="529" documentId="11_BA4204BCF9D61C042E83A027A8BF2034973450B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB5F71F-1356-4821-89E4-4146BCC6E2C2}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="191">
   <si>
     <t>Command</t>
   </si>
@@ -845,13 +845,29 @@
     <t>バカに正論は通じないからだ。
 こういう時は適当に話を逸らすんだ</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM_不穏</t>
+  </si>
+  <si>
+    <t>BGM_日常コミカル</t>
+  </si>
+  <si>
+    <t>BGM_緊迫</t>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,13 +903,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <family val="3"/>
@@ -921,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -933,11 +942,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -946,8 +954,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1172,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1076"/>
+  <dimension ref="A1:L1079"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1290,8 +1298,12 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
@@ -1354,14 +1366,14 @@
       <c r="B16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="12" t="b">
+      <c r="C16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C17" s="1"/>
@@ -1372,7 +1384,7 @@
     </row>
     <row r="18" spans="1:10" ht="28.8" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I18" s="5" t="s">
@@ -1381,7 +1393,7 @@
     </row>
     <row r="19" spans="1:10" ht="28.8" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I19" s="5" t="s">
@@ -1390,7 +1402,7 @@
     </row>
     <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I20" s="5" t="s">
@@ -1399,7 +1411,7 @@
     </row>
     <row r="21" spans="1:10" ht="28.8" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>75</v>
       </c>
       <c r="H21" s="1"/>
@@ -1408,7 +1420,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="1"/>
@@ -1417,7 +1429,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="1"/>
@@ -1427,7 +1439,7 @@
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I24" s="5" t="s">
@@ -1437,7 +1449,7 @@
     </row>
     <row r="25" spans="1:10" ht="28.2" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -1446,7 +1458,7 @@
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="27" customHeight="1">
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="1"/>
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="1"/>
@@ -1465,7 +1477,7 @@
     </row>
     <row r="28" spans="1:10" ht="28.8" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -1475,7 +1487,7 @@
     </row>
     <row r="29" spans="1:10" ht="30.6" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I29" s="5" t="s">
@@ -1484,7 +1496,7 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I30" s="5" t="s">
@@ -1492,7 +1504,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I31" s="5" t="s">
@@ -1500,7 +1512,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I32" s="5" t="s">
@@ -1508,7 +1520,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I33" s="5" t="s">
@@ -1516,7 +1528,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I35" s="5" t="s">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I36" s="5" t="s">
@@ -1540,7 +1552,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I37" s="5" t="s">
@@ -1548,7 +1560,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="1"/>
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="30" customHeight="1">
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="1"/>
@@ -1566,7 +1578,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I40" s="5" t="s">
@@ -1574,34 +1586,34 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B41" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11"/>
+      <c r="B41" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="10"/>
       <c r="I41" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>22</v>
       </c>
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I44" s="8" t="s">
+      <c r="I44" s="7" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1611,7 +1623,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="30" customHeight="1">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="8" t="s">
         <v>60</v>
       </c>
       <c r="I46" s="5"/>
@@ -1622,7 +1634,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I48" s="5" t="s">
@@ -1630,1263 +1642,1288 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>64</v>
       </c>
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="12" t="s">
+      <c r="A50" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I51" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="B51" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="9" t="s">
+    <row r="52" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I51" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52" s="9" t="s">
+    <row r="53" spans="1:10" ht="30" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I52" s="5" t="s">
+      <c r="I53" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B53" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="9" t="s">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B54" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I54" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B54" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" s="12" t="s">
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B55" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="I55" s="5" t="s">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B56" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="I56" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I56" s="5" t="s">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="30" customHeight="1">
-      <c r="A57" s="1"/>
-      <c r="B57" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I57" s="5" t="s">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="30" customHeight="1">
+      <c r="A58" s="1"/>
+      <c r="B58" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="30" customHeight="1">
-      <c r="B58" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="30" customHeight="1">
+      <c r="B59" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I59" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B59" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" s="10" t="s">
+    <row r="60" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B60" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I59" s="5" t="s">
+      <c r="I60" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A60" s="12" t="s">
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A61" s="12" t="s">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="I62" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" ht="30" customHeight="1">
-      <c r="B63" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" s="10" t="s">
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" ht="30" customHeight="1">
+      <c r="B64" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A64" s="12" t="s">
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A65" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A65" s="1" t="s">
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:9" ht="30" customHeight="1">
-      <c r="B66" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" ht="30" customHeight="1">
+      <c r="B67" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="I67" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A67" s="12" t="s">
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A68" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" ht="30" customHeight="1">
-      <c r="B69" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" s="10" t="s">
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" ht="30" customHeight="1">
+      <c r="B70" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I69" s="5" t="s">
+      <c r="I70" s="5" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28.8" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C71" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="5" t="s">
+      <c r="H72" s="1"/>
+      <c r="I72" s="5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A72" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C72" s="9"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="5"/>
     </row>
     <row r="73" spans="1:9" ht="28.8" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C73" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C73" s="8"/>
       <c r="H73" s="1"/>
       <c r="I73" s="5"/>
     </row>
-    <row r="74" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B74" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="I74" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B75" s="11" t="s">
+    <row r="74" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B75" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C75" s="1"/>
       <c r="I75" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B76" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="I76" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C76" s="10" t="s">
+    <row r="77" spans="1:9" ht="30" customHeight="1">
+      <c r="A77" s="1"/>
+      <c r="B77" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I77" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C77" s="9" t="s">
+    <row r="78" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A78" s="1"/>
+      <c r="B78" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H77" s="1"/>
-      <c r="I77" s="5" t="s">
+      <c r="H78" s="1"/>
+      <c r="I78" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B78" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C78" s="9" t="s">
+    <row r="79" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B79" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I79" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B79" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C79" s="9" t="s">
+    <row r="80" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B80" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I80" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B80" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C80" s="9" t="s">
+    <row r="81" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B81" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I80" s="5" t="s">
+      <c r="I81" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="12" t="s">
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I81" s="5" t="s">
+      <c r="I82" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A82" s="12" t="s">
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="1"/>
-      <c r="I82" s="5" t="s">
+      <c r="C83" s="1"/>
+      <c r="I83" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B84" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C84" s="10" t="s">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B85" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C85" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I84" s="5" t="s">
+      <c r="I85" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A85" s="12" t="s">
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A86" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="31.2" customHeight="1">
-      <c r="B87" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" s="10" t="s">
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B88" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C88" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="I88" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A88" s="12" t="s">
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A89" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A89" s="1" t="s">
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A90" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="30" customHeight="1">
-      <c r="A90" s="1"/>
-      <c r="B90" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C90" s="10" t="s">
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="30" customHeight="1">
+      <c r="A91" s="1"/>
+      <c r="B91" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="5" t="s">
+      <c r="I91" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A91" s="1"/>
-      <c r="B91" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C91" s="10" t="s">
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A92" s="1"/>
+      <c r="B92" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I91" s="5" t="s">
+      <c r="I92" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A92" s="1"/>
-      <c r="B92" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C92" s="10" t="s">
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A93" s="1"/>
+      <c r="B93" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I92" s="13" t="s">
+      <c r="I93" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B93" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C93" s="10" t="s">
+    <row r="94" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B94" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C94" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="I94" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B94" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C94" s="10" t="s">
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B95" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C95" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I94" s="5" t="s">
+      <c r="I95" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="12" t="s">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="I95" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C96" s="1"/>
       <c r="I96" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="I97" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A98" s="12" t="s">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A99" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="I100" s="1"/>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="I101" s="1"/>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B102" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C102" s="10" t="s">
+      <c r="A102" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B103" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C103" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="6" t="s">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B104" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C103" s="10"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="12" t="s">
+      <c r="C104" s="9"/>
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B105" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="12" t="s">
+      <c r="C105" s="9"/>
+      <c r="D105" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A105" s="1"/>
-      <c r="B105" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I105" s="12" t="s">
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A106" s="1"/>
+      <c r="B106" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I106" s="11" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="30" customHeight="1">
-      <c r="A106" s="1"/>
-      <c r="B106" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I106" s="13" t="s">
+    <row r="107" spans="1:9" ht="30" customHeight="1">
+      <c r="A107" s="1"/>
+      <c r="B107" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107" s="12" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B107" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C107" s="10" t="s">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B108" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C108" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I107" s="12" t="s">
+      <c r="I108" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B108" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C108" s="10" t="s">
+    <row r="109" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B109" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C109" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A109" s="12" t="s">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A110" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I109" s="12" t="s">
+      <c r="I110" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A111" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B111" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C111" s="10" t="s">
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B112" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C112" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I111" s="5" t="s">
+      <c r="I112" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B112" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C112" s="10" t="s">
+    <row r="113" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B113" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C113" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="I113" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="30" customHeight="1">
-      <c r="B113" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="I113" s="5" t="s">
+    <row r="114" spans="1:10" ht="30" customHeight="1">
+      <c r="B114" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="I114" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B114" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I114" s="5" t="s">
+    <row r="115" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B115" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B115" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C115" s="9" t="s">
+    <row r="116" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B116" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I115" s="5" t="s">
+      <c r="I116" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B116" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C116" s="9" t="s">
+    <row r="117" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B117" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I116" s="5" t="s">
+      <c r="I117" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="30" customHeight="1">
-      <c r="B117" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C117" s="9" t="s">
+    <row r="118" spans="1:10" ht="30" customHeight="1">
+      <c r="B118" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C118" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I117" s="5" t="s">
+      <c r="I118" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B118" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="I118" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="30" customHeight="1">
-      <c r="B119" s="11" t="s">
+    <row r="119" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B119" s="10" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="1"/>
       <c r="I119" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A120" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="30" customHeight="1">
+      <c r="B120" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C120" s="1"/>
       <c r="I120" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="I121" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A121" s="1" t="s">
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A122" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="30" customHeight="1">
-      <c r="B122" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C122" s="9" t="s">
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="30" customHeight="1">
+      <c r="B123" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C123" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I122" s="5" t="s">
+      <c r="I123" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A123" s="1"/>
-      <c r="B123" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C123" s="9" t="s">
+    <row r="124" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A124" s="1"/>
+      <c r="B124" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C124" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I123" s="5" t="s">
+      <c r="I124" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A124" s="1"/>
-      <c r="B124" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I124" s="5" t="s">
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A125" s="1"/>
+      <c r="B125" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I125" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" ht="30" customHeight="1">
-      <c r="A125" s="1"/>
-      <c r="B125" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I125" s="5" t="s">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="30" customHeight="1">
+      <c r="A126" s="1"/>
+      <c r="B126" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" ht="30" customHeight="1">
-      <c r="B126" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C126" s="1"/>
-      <c r="I126" s="5" t="s">
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="30" customHeight="1">
+      <c r="B127" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="I127" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A127" s="1"/>
-      <c r="B127" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I127" s="13" t="s">
+    <row r="128" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I128" s="12" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A128" s="1"/>
-      <c r="B128" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I128" s="13" t="s">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A129" s="1"/>
+      <c r="B129" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I129" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="12" t="s">
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A130" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="I129" s="13" t="s">
+      <c r="C130" s="1"/>
+      <c r="I130" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A131" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="I130" s="1"/>
-    </row>
-    <row r="131" spans="1:10" ht="30" customHeight="1">
-      <c r="B131" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C131" s="10" t="s">
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="30" customHeight="1">
+      <c r="B132" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I131" s="5" t="s">
+      <c r="I132" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A132" s="12" t="s">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I132" s="5" t="s">
+      <c r="I133" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B134" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C134" s="10" t="s">
+      <c r="B134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B135" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C135" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I134" s="5" t="s">
+      <c r="I135" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B135" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C135" s="10" t="s">
+    <row r="136" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B136" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C136" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I135" s="5" t="s">
+      <c r="I136" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A136" s="1"/>
-      <c r="B136" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C136" s="10" t="s">
+    <row r="137" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A137" s="1"/>
+      <c r="B137" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C137" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I136" s="13" t="s">
+      <c r="I137" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A137" s="1"/>
-      <c r="B137" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C137" s="10" t="s">
+    <row r="138" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I137" s="13" t="s">
+      <c r="I138" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="30" customHeight="1">
-      <c r="B138" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C138" s="10" t="s">
+    <row r="139" spans="1:10" ht="30" customHeight="1">
+      <c r="B139" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C139" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I138" s="5" t="s">
+      <c r="I139" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A139" s="12" t="s">
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I139" s="5" t="s">
+      <c r="I140" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A140" s="1" t="s">
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A141" s="1"/>
-      <c r="B141" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C141" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H141" s="1"/>
-      <c r="I141" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+    <row r="142" spans="1:10" ht="30.6" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="B142" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C142" s="9" t="s">
+      <c r="B142" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H142" s="1"/>
       <c r="I142" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H143" s="1"/>
+      <c r="I143" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B143" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C143" s="10" t="s">
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B144" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I143" s="5" t="s">
+      <c r="I144" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B144" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C144" s="10" t="s">
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A145" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C145" s="9"/>
+      <c r="I145" s="5"/>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B146" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C146" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I144" s="5" t="s">
+      <c r="I146" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A145" s="12" t="s">
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A147" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I145" s="5" t="s">
+      <c r="I147" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A146" s="1" t="s">
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A148" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B147" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C147" s="10" t="s">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B149" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C149" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I147" s="5" t="s">
+      <c r="I149" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A148" s="6" t="s">
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B150" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C148" s="10"/>
-      <c r="I148" s="5"/>
-    </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B149" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I149" s="5" t="s">
+      <c r="C150" s="9"/>
+      <c r="I150" s="5"/>
+    </row>
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B151" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I151" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A150" s="12" t="s">
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A152" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I150" s="5" t="s">
+      <c r="I152" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A151" s="1" t="s">
+    <row r="153" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A153" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A152" s="6" t="s">
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A154" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B152" s="12" t="s">
+      <c r="B154" s="11" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A153" s="12" t="s">
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A155" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B153" s="10" t="s">
+      <c r="B155" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C153" s="10"/>
-      <c r="D153" s="12" t="s">
+      <c r="C155" s="9"/>
+      <c r="D155" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B154" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I154" s="13" t="s">
+    <row r="156" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B156" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I156" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B155" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I155" s="13" t="s">
+    <row r="157" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B157" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I157" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="30" customHeight="1">
-      <c r="B156" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C156" s="9" t="s">
+    <row r="158" spans="1:9" ht="30" customHeight="1">
+      <c r="B158" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C158" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I156" s="13" t="s">
+      <c r="I158" s="12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B157" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I157" s="13" t="s">
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B159" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I159" s="12" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B158" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C158" s="9" t="s">
+    <row r="160" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B160" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C160" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I158" s="13" t="s">
+      <c r="I160" s="12" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B159" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I159" s="13" t="s">
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B161" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I161" s="12" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B160" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C160" s="9" t="s">
+    <row r="162" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B162" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C162" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I160" s="13" t="s">
+      <c r="I162" s="12" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B161" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I161" s="13" t="s">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B163" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I163" s="12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B162" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C162" s="9" t="s">
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A164" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I164" s="12"/>
+    </row>
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B165" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C165" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I162" s="13" t="s">
+      <c r="I165" s="12" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B163" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I163" s="13" t="s">
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B166" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I166" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B164" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C164" s="9" t="s">
+    <row r="167" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B167" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C167" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I164" s="13" t="s">
+      <c r="I167" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A165" s="6" t="s">
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A168" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B168" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="I165" s="13"/>
-    </row>
-    <row r="166" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C166" s="9" t="s">
+      <c r="I168" s="12"/>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A169" s="6"/>
+      <c r="B169" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C169" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="I166" s="13"/>
-    </row>
-    <row r="167" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I167" s="13" t="s">
+      <c r="I169" s="12"/>
+    </row>
+    <row r="170" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I170" s="12" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A168" s="11" t="s">
+    <row r="171" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A171" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B171" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="I168" s="13"/>
-    </row>
-    <row r="169" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A169" s="10" t="s">
+      <c r="I171" s="12"/>
+    </row>
+    <row r="172" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A172" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B169" s="10" t="s">
+      <c r="B172" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="G169">
+      <c r="G172">
         <v>1</v>
       </c>
-      <c r="I169" s="13"/>
-    </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I170" s="13" t="s">
+      <c r="I172" s="12"/>
+    </row>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I173" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A175" s="1" t="s">
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="178" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A178" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="177" ht="13.5" customHeight="1"/>
-    <row r="178" ht="13.5" customHeight="1"/>
-    <row r="179" ht="13.5" customHeight="1"/>
-    <row r="180" ht="13.5" customHeight="1"/>
-    <row r="181" ht="13.5" customHeight="1"/>
-    <row r="182" ht="13.5" customHeight="1"/>
-    <row r="183" ht="13.5" customHeight="1"/>
-    <row r="184" ht="13.5" customHeight="1"/>
-    <row r="185" ht="13.5" customHeight="1"/>
-    <row r="186" ht="13.5" customHeight="1"/>
-    <row r="187" ht="13.5" customHeight="1"/>
-    <row r="188" ht="13.5" customHeight="1"/>
-    <row r="189" ht="13.5" customHeight="1"/>
-    <row r="190" ht="13.5" customHeight="1"/>
-    <row r="191" ht="13.5" customHeight="1"/>
-    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="179" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="192" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="193" ht="13.5" customHeight="1"/>
     <row r="194" ht="13.5" customHeight="1"/>
     <row r="195" ht="13.5" customHeight="1"/>
@@ -3771,6 +3808,9 @@
     <row r="1074" ht="13.5" customHeight="1"/>
     <row r="1075" ht="13.5" customHeight="1"/>
     <row r="1076" ht="13.5" customHeight="1"/>
+    <row r="1077" ht="13.5" customHeight="1"/>
+    <row r="1078" ht="13.5" customHeight="1"/>
+    <row r="1079" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
